--- a/data/raw/Retos/Plan de retos.xlsx
+++ b/data/raw/Retos/Plan de retos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Retos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Retos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="8_{D4183C01-A731-46D5-A9D4-97CA5D131F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E91D01F-EC37-429D-86B8-3109241F88D7}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="8_{D4183C01-A731-46D5-A9D4-97CA5D131F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85306502-9BD0-46EC-A278-DD7AD31011E8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{557E1470-D854-4955-8C66-3C30D44953A5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="25">
   <si>
     <t>Línea Estratégica</t>
   </si>
@@ -296,7 +296,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -324,6 +324,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -782,8 +784,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0D56B507-94F7-45AC-A862-EDB1AC90037F}" name="Tabla3" displayName="Tabla3" ref="A1:E25" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
-  <autoFilter ref="A1:E25" xr:uid="{0D56B507-94F7-45AC-A862-EDB1AC90037F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0D56B507-94F7-45AC-A862-EDB1AC90037F}" name="Tabla3" displayName="Tabla3" ref="A1:E31" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
+  <autoFilter ref="A1:E31" xr:uid="{0D56B507-94F7-45AC-A862-EDB1AC90037F}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8B271B2D-A4E0-422B-BE09-F1E0B81A44F3}" name="Línea Estratégica" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{C2649D08-0C0E-4C27-A4AD-536F3275B631}" name="Año" dataDxfId="13"/>
@@ -1153,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F22B49E-A1AC-4D8D-9BB2-1117821941A9}">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.33203125" bestFit="1" customWidth="1"/>
@@ -1620,6 +1622,114 @@
       <c r="E25" s="9">
         <f t="shared" si="0"/>
         <v>0.79421686746987941</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2">
+        <v>2022</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.95350000000000001</v>
+      </c>
+      <c r="E26" s="23">
+        <f t="shared" ref="E26:E31" si="1">IF(D26/C26&gt;1,1,D26/C26)</f>
+        <v>0.95350000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2022</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0.96960000000000002</v>
+      </c>
+      <c r="E27" s="23">
+        <f t="shared" si="1"/>
+        <v>0.96960000000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="2">
+        <v>2022</v>
+      </c>
+      <c r="C28" s="4">
+        <v>1</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0.96140000000000003</v>
+      </c>
+      <c r="E28" s="23">
+        <f t="shared" si="1"/>
+        <v>0.96140000000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="2">
+        <v>2022</v>
+      </c>
+      <c r="C29" s="4">
+        <v>1</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0.99970000000000003</v>
+      </c>
+      <c r="E29" s="23">
+        <f t="shared" si="1"/>
+        <v>0.99970000000000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="2">
+        <v>2022</v>
+      </c>
+      <c r="C30" s="4">
+        <v>1</v>
+      </c>
+      <c r="D30" s="6">
+        <v>0.98</v>
+      </c>
+      <c r="E30" s="23">
+        <f t="shared" si="1"/>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2022</v>
+      </c>
+      <c r="C31" s="16">
+        <v>1</v>
+      </c>
+      <c r="D31" s="22">
+        <v>0.83289999999999997</v>
+      </c>
+      <c r="E31" s="24">
+        <f t="shared" si="1"/>
+        <v>0.83289999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/Retos/Plan de retos.xlsx
+++ b/data/raw/Retos/Plan de retos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SGING/data/raw/Retos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="8_{D4183C01-A731-46D5-A9D4-97CA5D131F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85306502-9BD0-46EC-A278-DD7AD31011E8}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="8_{D4183C01-A731-46D5-A9D4-97CA5D131F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F8C7ED9-2DD4-4C8B-8A29-F39D0A46A08F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{557E1470-D854-4955-8C66-3C30D44953A5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{557E1470-D854-4955-8C66-3C30D44953A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Linea" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="25">
   <si>
     <t>Línea Estratégica</t>
   </si>
@@ -324,14 +324,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="20">
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -784,14 +787,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0D56B507-94F7-45AC-A862-EDB1AC90037F}" name="Tabla3" displayName="Tabla3" ref="A1:E31" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0D56B507-94F7-45AC-A862-EDB1AC90037F}" name="Tabla3" displayName="Tabla3" ref="A1:E31" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
   <autoFilter ref="A1:E31" xr:uid="{0D56B507-94F7-45AC-A862-EDB1AC90037F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8B271B2D-A4E0-422B-BE09-F1E0B81A44F3}" name="Línea Estratégica" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{C2649D08-0C0E-4C27-A4AD-536F3275B631}" name="Año" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{D949FAD6-480B-4FDA-9AE8-31D46A8ED7B5}" name="Meta" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{7663C50E-80CF-4F20-9587-4EAA4F1B329E}" name="Ejecución" dataDxfId="11" dataCellStyle="Porcentaje"/>
-    <tableColumn id="5" xr3:uid="{FA88A2D1-6122-4340-9A57-12F7D7AD2114}" name="Cumplimiento" dataDxfId="10" dataCellStyle="Porcentaje">
+    <tableColumn id="1" xr3:uid="{8B271B2D-A4E0-422B-BE09-F1E0B81A44F3}" name="Línea Estratégica" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{C2649D08-0C0E-4C27-A4AD-536F3275B631}" name="Año" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{D949FAD6-480B-4FDA-9AE8-31D46A8ED7B5}" name="Meta" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{7663C50E-80CF-4F20-9587-4EAA4F1B329E}" name="Ejecución" dataDxfId="12" dataCellStyle="Porcentaje"/>
+    <tableColumn id="5" xr3:uid="{FA88A2D1-6122-4340-9A57-12F7D7AD2114}" name="Cumplimiento" dataDxfId="11" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(D2/C2&gt;1,1,D2/C2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -800,15 +803,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{06F90347-0855-4383-9569-33279D7F9297}" name="Tabla2" displayName="Tabla2" ref="A1:F45" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{06F90347-0855-4383-9569-33279D7F9297}" name="Tabla2" displayName="Tabla2" ref="A1:F45" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:F45" xr:uid="{06F90347-0855-4383-9569-33279D7F9297}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{22977429-7756-49B9-8F1C-59D1D94ADD97}" name="Línea Estratégica" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{C0147790-F88D-4586-A14D-912D57FA7C78}" name="Objetivo" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{0361A927-7B9F-4D80-95CD-00AA32B4B4E9}" name="Año" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{6EC61543-8E4A-4D24-A5D7-28C80DC56C56}" name="Meta" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{D180F852-CE12-4DC1-8BBC-10FFE646B4E1}" name="Ejecución" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{E7063ED5-D130-42FD-A7A0-2D1D9802D166}" name="Cumplimiento" dataDxfId="0" dataCellStyle="Porcentaje">
+    <tableColumn id="1" xr3:uid="{22977429-7756-49B9-8F1C-59D1D94ADD97}" name="Línea Estratégica" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{C0147790-F88D-4586-A14D-912D57FA7C78}" name="Objetivo" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{0361A927-7B9F-4D80-95CD-00AA32B4B4E9}" name="Año" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{6EC61543-8E4A-4D24-A5D7-28C80DC56C56}" name="Meta" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{D180F852-CE12-4DC1-8BBC-10FFE646B4E1}" name="Ejecución" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{E7063ED5-D130-42FD-A7A0-2D1D9802D166}" name="Cumplimiento" dataDxfId="1" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>IF(E2/D2&gt;1,1,Tabla2[[#This Row],[Ejecución]]/Tabla2[[#This Row],[Meta]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -828,11 +831,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{36859B46-A924-485F-BA67-2AB7CF75A0BD}" name="Tabla4" displayName="Tabla4" ref="A1:B6" totalsRowShown="0">
-  <autoFilter ref="A1:B6" xr:uid="{36859B46-A924-485F-BA67-2AB7CF75A0BD}"/>
-  <tableColumns count="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{36859B46-A924-485F-BA67-2AB7CF75A0BD}" name="Tabla4" displayName="Tabla4" ref="A1:E6" totalsRowShown="0">
+  <autoFilter ref="A1:E6" xr:uid="{36859B46-A924-485F-BA67-2AB7CF75A0BD}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{97246F26-F740-47DC-A136-932AD3FF683D}" name="Año"/>
     <tableColumn id="2" xr3:uid="{D14DD27A-5F2E-4A19-BD94-2116649FC976}" name="N°"/>
+    <tableColumn id="3" xr3:uid="{9E49BD03-9AB6-4B40-88BD-B02179FBFC21}" name="Meta"/>
+    <tableColumn id="4" xr3:uid="{394983A4-5C08-4CA1-AC84-F35636D0AEF5}" name="Ejecución"/>
+    <tableColumn id="5" xr3:uid="{F9465BFF-545C-4D4E-A930-DAF15FE92FCC}" name="Cumplimiento" dataDxfId="0">
+      <calculatedColumnFormula>Tabla4[[#This Row],[Ejecución]]/Tabla4[[#This Row],[Meta]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1637,7 +1645,7 @@
       <c r="D26" s="6">
         <v>0.95350000000000001</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="9">
         <f t="shared" ref="E26:E31" si="1">IF(D26/C26&gt;1,1,D26/C26)</f>
         <v>0.95350000000000001</v>
       </c>
@@ -1655,7 +1663,7 @@
       <c r="D27" s="6">
         <v>0.96960000000000002</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="9">
         <f t="shared" si="1"/>
         <v>0.96960000000000002</v>
       </c>
@@ -1673,7 +1681,7 @@
       <c r="D28" s="6">
         <v>0.96140000000000003</v>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="9">
         <f t="shared" si="1"/>
         <v>0.96140000000000003</v>
       </c>
@@ -1691,7 +1699,7 @@
       <c r="D29" s="6">
         <v>0.99970000000000003</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="9">
         <f t="shared" si="1"/>
         <v>0.99970000000000003</v>
       </c>
@@ -1709,7 +1717,7 @@
       <c r="D30" s="6">
         <v>0.98</v>
       </c>
-      <c r="E30" s="23">
+      <c r="E30" s="9">
         <f t="shared" si="1"/>
         <v>0.98</v>
       </c>
@@ -1727,7 +1735,7 @@
       <c r="D31" s="22">
         <v>0.83289999999999997</v>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="18">
         <f t="shared" si="1"/>
         <v>0.83289999999999997</v>
       </c>
@@ -2996,55 +3004,114 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFEF2421-346E-4A38-9990-7BD73E815025}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2022</v>
       </c>
       <c r="B2">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" s="23">
+        <v>1</v>
+      </c>
+      <c r="D2" s="24">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="E2" s="24">
+        <f>Tabla4[[#This Row],[Ejecución]]/Tabla4[[#This Row],[Meta]]</f>
+        <v>0.96299999999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2023</v>
       </c>
       <c r="B3">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C3" s="23">
+        <v>1</v>
+      </c>
+      <c r="D3" s="23">
+        <v>0.97</v>
+      </c>
+      <c r="E3" s="24">
+        <f>Tabla4[[#This Row],[Ejecución]]/Tabla4[[#This Row],[Meta]]</f>
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2024</v>
       </c>
       <c r="B4">
         <v>83</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C4" s="23">
+        <v>1</v>
+      </c>
+      <c r="D4" s="23">
+        <v>0.98</v>
+      </c>
+      <c r="E4" s="24">
+        <f>Tabla4[[#This Row],[Ejecución]]/Tabla4[[#This Row],[Meta]]</f>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2025</v>
       </c>
       <c r="B5">
         <v>84</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C5" s="23">
+        <v>1</v>
+      </c>
+      <c r="D5" s="23">
+        <v>0.99</v>
+      </c>
+      <c r="E5" s="24">
+        <f>Tabla4[[#This Row],[Ejecución]]/Tabla4[[#This Row],[Meta]]</f>
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2026</v>
       </c>
       <c r="B6">
         <v>88</v>
+      </c>
+      <c r="C6" s="23">
+        <v>1</v>
+      </c>
+      <c r="D6" s="23">
+        <v>0.99</v>
+      </c>
+      <c r="E6" s="24">
+        <f>Tabla4[[#This Row],[Ejecución]]/Tabla4[[#This Row],[Meta]]</f>
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
